--- a/Template_Outage_EIC_Monitoring_unit 2.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 2.xlsx
@@ -23489,7 +23489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:P93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -23581,6 +23581,11 @@
           <t>Photo_Count</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>No_WO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23628,6 +23633,11 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>WO-180726-0026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23675,6 +23685,11 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>WO-180726-0026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23717,6 +23732,11 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>WO-180726-0027</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23759,6 +23779,11 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>WO-180726-0027</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23801,6 +23826,11 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>WO-180726-0027</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23843,6 +23873,11 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>WO-180726-0027</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23890,6 +23925,11 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>WO-180726-0017</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23937,6 +23977,11 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>WO-180726-0018</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23984,6 +24029,11 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>WO-180726-0007</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24031,6 +24081,11 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>WO-180726-0008</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24078,6 +24133,11 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>WO-180726-0007</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24125,6 +24185,11 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>WO-180726-0008</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24172,6 +24237,11 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>WO-180726-0007</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24219,6 +24289,11 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>WO-180726-0008</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24261,6 +24336,11 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>WO-180726-0009</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24303,6 +24383,11 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>WO-180726-0009</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24350,6 +24435,11 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>WO-180726-0026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24402,6 +24492,11 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24449,6 +24544,11 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>WO-180726-0026</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24501,6 +24601,11 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24543,6 +24648,11 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>WO-180726-0024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24585,6 +24695,11 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>WO-180726-0025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -24627,6 +24742,11 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>WO-180726-0024</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -24674,6 +24794,11 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>WO-180726-0013</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -24721,6 +24846,11 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>WO-180726-0015</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -24768,6 +24898,11 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -24820,6 +24955,11 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -24872,6 +25012,11 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -24919,6 +25064,11 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -24966,6 +25116,11 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>WO-180726-0055</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -25013,6 +25168,11 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -25060,6 +25220,11 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -25102,6 +25267,11 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>WO-180726-0055</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -25149,6 +25319,11 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>WO-180726-0055</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -25196,6 +25371,11 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -25243,6 +25423,11 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -25290,6 +25475,11 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>WO-180726-0055</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -25332,6 +25522,11 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>WO-180726-0041</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -25374,6 +25569,11 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>WO-180726-0041</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -25421,6 +25621,11 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -25468,6 +25673,11 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -25510,6 +25720,11 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -25552,6 +25767,11 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -25594,6 +25814,11 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -25636,6 +25861,11 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25678,6 +25908,11 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -25720,6 +25955,11 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -25762,6 +26002,11 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -25804,6 +26049,11 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -25846,6 +26096,11 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>WO-180726-0009</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -25888,6 +26143,11 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>WO-180726-0009</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -25930,6 +26190,11 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>WO-180726-0009</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -25972,6 +26237,11 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>WO-180726-0009</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -26019,6 +26289,11 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>WO-180726-0046</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -26071,6 +26346,11 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>WO-180726-0051</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -26118,6 +26398,11 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>WO-180726-0051</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -26170,6 +26455,11 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>WO-180726-0061</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -26222,6 +26512,11 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>WO-180726-0061</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -26269,6 +26564,11 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>WO-180726-0046</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -26311,6 +26611,11 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>WO-180726-0051</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -26358,6 +26663,11 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>WO-180726-0048</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -26400,6 +26710,11 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -26447,6 +26762,11 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>WO-180726-0047</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -26494,6 +26814,11 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>WO-180726-0047</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -26541,6 +26866,11 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>WO-180726-0047</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -26593,6 +26923,11 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>WO-180726-0047</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -26640,6 +26975,11 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>WO-180726-0047</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -26687,6 +27027,11 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>WO-180726-0047</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -26734,6 +27079,11 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>WO-180726-0047</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -26776,6 +27126,11 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -26818,6 +27173,11 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -26860,6 +27220,11 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -26902,6 +27267,11 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -26944,6 +27314,11 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -26986,6 +27361,11 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -27028,6 +27408,11 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>WO-180726-0045</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -27070,6 +27455,11 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>WO-180726-0051</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -27117,6 +27507,11 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -27164,6 +27559,11 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>WO-180726-0020</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -27206,6 +27606,11 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -27248,6 +27653,11 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -27290,6 +27700,11 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -27332,6 +27747,11 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -27374,6 +27794,11 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -27416,6 +27841,11 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -27458,6 +27888,11 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -27500,6 +27935,11 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -27542,6 +27982,11 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -27584,6 +28029,11 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -27626,6 +28076,11 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -27668,6 +28123,11 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>WO-180726-0026</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -27709,6 +28169,11 @@
       </c>
       <c r="O93" t="n">
         <v>0</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>WO-180726-0026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -27723,7 +28188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27800,6 +28265,16 @@
           <t>Photo_Count</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Calibration_TRUE_FALSE</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>No_WO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -27834,6 +28309,11 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>WO-180726-0008</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -27867,6 +28347,11 @@
       </c>
       <c r="L3" t="n">
         <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>WO-180726-0007</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -27902,6 +28387,11 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>WO-180726-0007</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -27936,6 +28426,11 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>WO-180726-0007</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -27970,6 +28465,11 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -28004,6 +28504,11 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -28038,6 +28543,11 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -28072,6 +28582,11 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -28106,6 +28621,11 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -28140,6 +28660,11 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>WO-180726-0020</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -28174,6 +28699,11 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>WO-180726-0020</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -28208,6 +28738,11 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>WO-180726-0021</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -28242,6 +28777,11 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>WO-180726-0021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -28276,6 +28816,11 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -28310,6 +28855,11 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -28344,6 +28894,11 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -28378,6 +28933,11 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -28412,6 +28972,11 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>WO-180726-0009</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -28446,6 +29011,11 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>WO-180726-0011</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -28480,6 +29050,11 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>WO-180726-0013</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -28514,6 +29089,11 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>WO-180726-0015</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -28548,6 +29128,11 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -28582,6 +29167,11 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -28616,6 +29206,11 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>WO-180726-0026</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -28650,6 +29245,11 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>WO-180726-0026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -28684,6 +29284,11 @@
       <c r="L27" t="n">
         <v>0</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>WO-180726-0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -28718,6 +29323,11 @@
       <c r="L28" t="n">
         <v>0</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -28752,6 +29362,11 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -28786,6 +29401,11 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -28820,6 +29440,11 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>WO-180726-0040</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -28854,6 +29479,11 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>WO-180726-0027</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -28888,6 +29518,11 @@
       <c r="L33" t="n">
         <v>0</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -28922,6 +29557,11 @@
       <c r="L34" t="n">
         <v>0</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>WO-180726-0026</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -28956,6 +29596,11 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -28990,6 +29635,11 @@
       <c r="L36" t="n">
         <v>0</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -29024,6 +29674,11 @@
       <c r="L37" t="n">
         <v>0</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -29058,6 +29713,11 @@
       <c r="L38" t="n">
         <v>0</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -29092,6 +29752,11 @@
       <c r="L39" t="n">
         <v>0</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -29126,6 +29791,11 @@
       <c r="L40" t="n">
         <v>0</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -29160,6 +29830,11 @@
       <c r="L41" t="n">
         <v>0</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>WO-180726-0055</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -29194,6 +29869,11 @@
       <c r="L42" t="n">
         <v>0</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>WO-180726-0055</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -29228,6 +29908,11 @@
       <c r="L43" t="n">
         <v>0</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>WO-180726-0028</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -29262,6 +29947,11 @@
       <c r="L44" t="n">
         <v>0</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -29296,6 +29986,11 @@
       <c r="L45" t="n">
         <v>0</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -29330,6 +30025,11 @@
       <c r="L46" t="n">
         <v>0</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -29364,6 +30064,11 @@
       <c r="L47" t="n">
         <v>0</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -29398,6 +30103,11 @@
       <c r="L48" t="n">
         <v>0</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -29432,6 +30142,11 @@
       <c r="L49" t="n">
         <v>0</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -29466,6 +30181,11 @@
       <c r="L50" t="n">
         <v>0</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -29500,6 +30220,11 @@
       <c r="L51" t="n">
         <v>0</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -29534,6 +30259,11 @@
       <c r="L52" t="n">
         <v>0</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -29568,6 +30298,11 @@
       <c r="L53" t="n">
         <v>0</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -29602,6 +30337,11 @@
       <c r="L54" t="n">
         <v>0</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -29636,6 +30376,11 @@
       <c r="L55" t="n">
         <v>0</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -29670,6 +30415,11 @@
       <c r="L56" t="n">
         <v>0</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -29704,6 +30454,11 @@
       <c r="L57" t="n">
         <v>0</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -29738,6 +30493,11 @@
       <c r="L58" t="n">
         <v>0</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -29772,6 +30532,11 @@
       <c r="L59" t="n">
         <v>0</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -29806,6 +30571,11 @@
       <c r="L60" t="n">
         <v>0</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -29840,6 +30610,11 @@
       <c r="L61" t="n">
         <v>0</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -29874,6 +30649,11 @@
       <c r="L62" t="n">
         <v>0</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -29908,6 +30688,11 @@
       <c r="L63" t="n">
         <v>0</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -29942,6 +30727,11 @@
       <c r="L64" t="n">
         <v>0</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>WO-180726-0046</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -29976,6 +30766,11 @@
       <c r="L65" t="n">
         <v>0</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -30010,6 +30805,11 @@
       <c r="L66" t="n">
         <v>0</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>WO-180726-0051</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -30044,6 +30844,11 @@
       <c r="L67" t="n">
         <v>0</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -30078,6 +30883,11 @@
       <c r="L68" t="n">
         <v>0</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -30112,6 +30922,11 @@
       <c r="L69" t="n">
         <v>0</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -30146,6 +30961,11 @@
       <c r="L70" t="n">
         <v>0</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -30180,6 +31000,11 @@
       <c r="L71" t="n">
         <v>0</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -30214,6 +31039,11 @@
       <c r="L72" t="n">
         <v>0</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -30248,6 +31078,11 @@
       <c r="L73" t="n">
         <v>0</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -30282,6 +31117,11 @@
       <c r="L74" t="n">
         <v>0</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -30316,6 +31156,11 @@
       <c r="L75" t="n">
         <v>0</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -30350,6 +31195,11 @@
       <c r="L76" t="n">
         <v>0</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>WO-180726-0046</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -30384,6 +31234,11 @@
       <c r="L77" t="n">
         <v>0</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>WO-180726-0044</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -30418,6 +31273,11 @@
       <c r="L78" t="n">
         <v>0</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>WO-180726-0044</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -30452,6 +31312,11 @@
       <c r="L79" t="n">
         <v>0</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>WO-180726-0044</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -30486,6 +31351,11 @@
       <c r="L80" t="n">
         <v>0</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>WO-180726-0061</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -30520,6 +31390,11 @@
       <c r="L81" t="n">
         <v>0</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>WO-180726-0045</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -30554,6 +31429,11 @@
       <c r="L82" t="n">
         <v>0</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>WO-180726-0045</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -30588,6 +31468,11 @@
       <c r="L83" t="n">
         <v>0</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>WO-180726-0045</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -30622,6 +31507,11 @@
       <c r="L84" t="n">
         <v>0</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>WO-180726-0045</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -30656,6 +31546,11 @@
       <c r="L85" t="n">
         <v>0</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>WO-180726-0045</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -30690,6 +31585,11 @@
       <c r="L86" t="n">
         <v>0</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -30724,6 +31624,11 @@
       <c r="L87" t="n">
         <v>0</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -30758,6 +31663,11 @@
       <c r="L88" t="n">
         <v>0</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -30791,6 +31701,11 @@
       </c>
       <c r="L89" t="n">
         <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>WO-180726-0045</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -30805,7 +31720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -30881,6 +31796,16 @@
           <t>Photo_Count</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Calibration_TRUE_FALSE</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>No_WO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -30915,6 +31840,11 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>WO-180726-0028</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -30948,6 +31878,11 @@
       </c>
       <c r="L3" t="n">
         <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>WO-180726-0028</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -30983,6 +31918,11 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>WO-180726-0028</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -31017,6 +31957,11 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>WO-180726-0027</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -31051,6 +31996,11 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>WO-180726-0007</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -31085,6 +32035,11 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>WO-180726-0007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -31119,6 +32074,11 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>WO-180726-0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -31153,6 +32113,11 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -31187,6 +32152,11 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -31221,6 +32191,11 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -31255,6 +32230,11 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>WO-180726-0040</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -31289,6 +32269,11 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -31323,6 +32308,11 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -31357,6 +32347,11 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -31391,6 +32386,11 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -31425,6 +32425,11 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -31459,6 +32464,11 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>WO-180726-0039</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -31493,6 +32503,11 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -31527,6 +32542,11 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -31561,6 +32581,11 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>WO-180726-0050</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -31595,6 +32620,11 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>WO-180726-0050</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -31629,6 +32659,11 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>WO-180726-0050</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -31663,6 +32698,11 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>WO-180726-0050</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -31697,6 +32737,11 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>WO-180726-0045</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -31731,6 +32776,11 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -31765,6 +32815,11 @@
       <c r="L27" t="n">
         <v>0</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -31799,6 +32854,11 @@
       <c r="L28" t="n">
         <v>0</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -31833,6 +32893,11 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -31867,6 +32932,11 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>WO-180726-0046</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -31901,6 +32971,11 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -31935,6 +33010,11 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>WO-180726-0033</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -31968,6 +33048,11 @@
       </c>
       <c r="L33" t="n">
         <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>WO-180726-0045</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -31982,7 +33067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -32105,6 +33190,16 @@
           <t>Photo_Count</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Calibration_TRUE_FALSE</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>No_WO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -32154,6 +33249,11 @@
       <c r="T2" t="n">
         <v>0</v>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -32202,6 +33302,11 @@
       </c>
       <c r="T3" t="n">
         <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -32252,6 +33357,11 @@
       <c r="T4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -32301,6 +33411,11 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -32350,6 +33465,11 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -32399,6 +33519,11 @@
       <c r="T7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>WO-180726-0020</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -32448,6 +33573,11 @@
       <c r="T8" t="n">
         <v>0</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>WO-180726-0020</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -32497,6 +33627,11 @@
       <c r="T9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>WO-180726-0020</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -32546,6 +33681,11 @@
       <c r="T10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -32595,6 +33735,11 @@
       <c r="T11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -32644,6 +33789,11 @@
       <c r="T12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -32693,6 +33843,11 @@
       <c r="T13" t="n">
         <v>0</v>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>WO-180726-0024</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -32742,6 +33897,11 @@
       <c r="T14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -32791,6 +33951,11 @@
       <c r="T15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>WO-180726-0019</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -32840,6 +34005,11 @@
       <c r="T16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>WO-180726-0010</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -32889,6 +34059,11 @@
       <c r="T17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>WO-180726-0010</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -32938,6 +34113,11 @@
       <c r="T18" t="n">
         <v>0</v>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>WO-180726-0010</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -32987,6 +34167,11 @@
       <c r="T19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>WO-180726-0010</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -33036,6 +34221,11 @@
       <c r="T20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>WO-180726-0012</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -33085,6 +34275,11 @@
       <c r="T21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>WO-180726-0012</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -33134,6 +34329,11 @@
       <c r="T22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>WO-180726-0012</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -33183,6 +34383,11 @@
       <c r="T23" t="n">
         <v>0</v>
       </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>WO-180726-0014</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -33232,6 +34437,11 @@
       <c r="T24" t="n">
         <v>0</v>
       </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>WO-180726-0014</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -33281,6 +34491,11 @@
       <c r="T25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>WO-180726-0014</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -33330,6 +34545,11 @@
       <c r="T26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>WO-180726-0014</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -33379,6 +34599,11 @@
       <c r="T27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>WO-180726-0014</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -33428,6 +34653,11 @@
       <c r="T28" t="n">
         <v>0</v>
       </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>WO-180726-0016</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -33477,6 +34707,11 @@
       <c r="T29" t="n">
         <v>0</v>
       </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>WO-180726-0016</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -33526,6 +34761,11 @@
       <c r="T30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>WO-180726-0016</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -33575,6 +34815,11 @@
       <c r="T31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>WO-180726-0016</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -33619,6 +34864,11 @@
       <c r="T32" t="n">
         <v>0</v>
       </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>WO-180726-0024</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -33663,6 +34913,11 @@
       <c r="T33" t="n">
         <v>0</v>
       </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>WO-180726-0025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -33706,6 +34961,11 @@
       </c>
       <c r="T34" t="n">
         <v>0</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>WO-180726-0042</t>
+        </is>
       </c>
     </row>
   </sheetData>
